--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/202.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/202.xlsx
@@ -426,13 +426,13 @@
         <v>-13.44843818497168</v>
       </c>
       <c r="E2">
-        <v>-9.474244443381133</v>
+        <v>-13.24156348289424</v>
       </c>
       <c r="F2">
-        <v>3.613380396078441</v>
+        <v>3.274820496593542</v>
       </c>
       <c r="G2">
-        <v>-10.27695415259219</v>
+        <v>-14.25040995173812</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.13073140183763</v>
       </c>
       <c r="E3">
-        <v>-10.12393555231358</v>
+        <v>-15.37836017120556</v>
       </c>
       <c r="F3">
-        <v>3.977583661746135</v>
+        <v>3.158096619507909</v>
       </c>
       <c r="G3">
-        <v>-9.483714335927425</v>
+        <v>-15.29893586657271</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.80231368056439</v>
       </c>
       <c r="E4">
-        <v>-10.08023124966556</v>
+        <v>-13.02531526360596</v>
       </c>
       <c r="F4">
-        <v>4.102321090763892</v>
+        <v>2.842850454804194</v>
       </c>
       <c r="G4">
-        <v>-10.1107746981574</v>
+        <v>-13.80031811185543</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.48435838376882</v>
       </c>
       <c r="E5">
-        <v>-10.44668895178827</v>
+        <v>-14.16122409826797</v>
       </c>
       <c r="F5">
-        <v>4.265217913814163</v>
+        <v>2.929087993017618</v>
       </c>
       <c r="G5">
-        <v>-8.656538116939586</v>
+        <v>-14.91593057677058</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.16648408067685</v>
       </c>
       <c r="E6">
-        <v>-9.819114909909276</v>
+        <v>-15.09429805365241</v>
       </c>
       <c r="F6">
-        <v>4.851646793536321</v>
+        <v>3.04117636288876</v>
       </c>
       <c r="G6">
-        <v>-8.155291727384075</v>
+        <v>-13.20067237723616</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.84375751975461</v>
       </c>
       <c r="E7">
-        <v>-12.9699591973362</v>
+        <v>-14.05955532832176</v>
       </c>
       <c r="F7">
-        <v>4.861617805979927</v>
+        <v>3.650466037500286</v>
       </c>
       <c r="G7">
-        <v>-8.970887658075544</v>
+        <v>-12.96287589115031</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.50542188581493</v>
       </c>
       <c r="E8">
-        <v>-13.72430786905992</v>
+        <v>-16.90923345186856</v>
       </c>
       <c r="F8">
-        <v>4.317245820548179</v>
+        <v>3.820464197875387</v>
       </c>
       <c r="G8">
-        <v>-8.03948553387483</v>
+        <v>-11.03853522226491</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.14501020515299</v>
       </c>
       <c r="E9">
-        <v>-13.26157028106013</v>
+        <v>-17.2098199710757</v>
       </c>
       <c r="F9">
-        <v>4.26927853578135</v>
+        <v>4.304267350571154</v>
       </c>
       <c r="G9">
-        <v>-6.135587483694431</v>
+        <v>-11.17102325474655</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.7544748957884</v>
       </c>
       <c r="E10">
-        <v>-14.29315213153343</v>
+        <v>-16.0082075070364</v>
       </c>
       <c r="F10">
-        <v>4.211858110405261</v>
+        <v>3.319360641759361</v>
       </c>
       <c r="G10">
-        <v>-6.489471559660364</v>
+        <v>-10.528741004127</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.32648349188007</v>
       </c>
       <c r="E11">
-        <v>-15.5343027021337</v>
+        <v>-18.78557948610273</v>
       </c>
       <c r="F11">
-        <v>4.628347426871189</v>
+        <v>3.333870555356617</v>
       </c>
       <c r="G11">
-        <v>-5.775069074467799</v>
+        <v>-11.12030900763045</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.857076320512677</v>
       </c>
       <c r="E12">
-        <v>-15.78843160649614</v>
+        <v>-17.19774705937125</v>
       </c>
       <c r="F12">
-        <v>4.57303174665672</v>
+        <v>3.553620837065249</v>
       </c>
       <c r="G12">
-        <v>-6.832526841167341</v>
+        <v>-10.29043800457365</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.344598055044736</v>
       </c>
       <c r="E13">
-        <v>-16.33477841009955</v>
+        <v>-19.62604614803032</v>
       </c>
       <c r="F13">
-        <v>4.663586467195632</v>
+        <v>3.702405256703039</v>
       </c>
       <c r="G13">
-        <v>-5.001391271394583</v>
+        <v>-9.614441158182165</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.805106148410639</v>
       </c>
       <c r="E14">
-        <v>-16.91908741130925</v>
+        <v>-18.21602425321001</v>
       </c>
       <c r="F14">
-        <v>4.844035502906719</v>
+        <v>4.088572939711963</v>
       </c>
       <c r="G14">
-        <v>-4.67644467398742</v>
+        <v>-8.981322497615325</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.255743795239205</v>
       </c>
       <c r="E15">
-        <v>-18.08816731807745</v>
+        <v>-22.06188514591216</v>
       </c>
       <c r="F15">
-        <v>4.842999759238021</v>
+        <v>3.528132674062166</v>
       </c>
       <c r="G15">
-        <v>-2.654333663690725</v>
+        <v>-7.40028209060681</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.718513595783962</v>
       </c>
       <c r="E16">
-        <v>-18.44622922938994</v>
+        <v>-21.89202208588444</v>
       </c>
       <c r="F16">
-        <v>5.346033852864968</v>
+        <v>3.499554700818061</v>
       </c>
       <c r="G16">
-        <v>-3.241601268538659</v>
+        <v>-7.553262399976532</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.21662412416303</v>
       </c>
       <c r="E17">
-        <v>-19.28748837426886</v>
+        <v>-23.87643562383765</v>
       </c>
       <c r="F17">
-        <v>5.291639889493285</v>
+        <v>4.089089227840396</v>
       </c>
       <c r="G17">
-        <v>-3.374774583946921</v>
+        <v>-7.26319571037113</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.768987717111727</v>
       </c>
       <c r="E18">
-        <v>-20.7520195107195</v>
+        <v>-21.13350268959966</v>
       </c>
       <c r="F18">
-        <v>5.926571346581691</v>
+        <v>4.080899884551658</v>
       </c>
       <c r="G18">
-        <v>-1.997246653419563</v>
+        <v>-5.626428890300062</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.396315434856006</v>
       </c>
       <c r="E19">
-        <v>-22.37466231714794</v>
+        <v>-25.20018556033783</v>
       </c>
       <c r="F19">
-        <v>5.892885921760294</v>
+        <v>4.036788923688923</v>
       </c>
       <c r="G19">
-        <v>-2.153133621772764</v>
+        <v>-6.29189489133112</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.110666285999525</v>
       </c>
       <c r="E20">
-        <v>-22.88755275478268</v>
+        <v>-26.14179568922674</v>
       </c>
       <c r="F20">
-        <v>5.452234004142507</v>
+        <v>4.215304254477258</v>
       </c>
       <c r="G20">
-        <v>-3.214689843849924</v>
+        <v>-5.546952623538779</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.919020629492331</v>
       </c>
       <c r="E21">
-        <v>-22.75783008835895</v>
+        <v>-26.8063130220603</v>
       </c>
       <c r="F21">
-        <v>6.281031653457601</v>
+        <v>3.982063965780913</v>
       </c>
       <c r="G21">
-        <v>-2.364502022818612</v>
+        <v>-3.142900663830828</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.821096632572071</v>
       </c>
       <c r="E22">
-        <v>-24.46617426538256</v>
+        <v>-27.32853211615084</v>
       </c>
       <c r="F22">
-        <v>6.479024983299926</v>
+        <v>4.337457075441018</v>
       </c>
       <c r="G22">
-        <v>-1.546601952431812</v>
+        <v>-4.748452350012108</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.810992128127727</v>
       </c>
       <c r="E23">
-        <v>-23.65363923113428</v>
+        <v>-27.59309009615295</v>
       </c>
       <c r="F23">
-        <v>6.271874665854531</v>
+        <v>4.902186016709824</v>
       </c>
       <c r="G23">
-        <v>-0.9829286056422635</v>
+        <v>-4.822558911908693</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.881339679610385</v>
       </c>
       <c r="E24">
-        <v>-24.85495281588907</v>
+        <v>-28.78692717032107</v>
       </c>
       <c r="F24">
-        <v>6.580150940824397</v>
+        <v>4.992116757118053</v>
       </c>
       <c r="G24">
-        <v>-1.11898871676077</v>
+        <v>-4.417569944453031</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.020571918618457</v>
       </c>
       <c r="E25">
-        <v>-26.36830995909041</v>
+        <v>-27.40252738143617</v>
       </c>
       <c r="F25">
-        <v>6.316102820955009</v>
+        <v>4.678531899919634</v>
       </c>
       <c r="G25">
-        <v>-0.3276690165087782</v>
+        <v>-3.465983424099382</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.218540313046897</v>
       </c>
       <c r="E26">
-        <v>-25.57474017398625</v>
+        <v>-29.1561698839585</v>
       </c>
       <c r="F26">
-        <v>6.325093519436958</v>
+        <v>5.41350605968635</v>
       </c>
       <c r="G26">
-        <v>-0.4081748629327749</v>
+        <v>-4.722295729706326</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.461083041144422</v>
       </c>
       <c r="E27">
-        <v>-25.4261066001065</v>
+        <v>-29.38435968920501</v>
       </c>
       <c r="F27">
-        <v>6.801302802268192</v>
+        <v>4.983773794355518</v>
       </c>
       <c r="G27">
-        <v>-0.7174857537579604</v>
+        <v>-3.72013731569477</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.733688949109615</v>
       </c>
       <c r="E28">
-        <v>-25.31980067277643</v>
+        <v>-29.28702014041014</v>
       </c>
       <c r="F28">
-        <v>6.395025221545017</v>
+        <v>5.125436288491577</v>
       </c>
       <c r="G28">
-        <v>-1.616891455321617</v>
+        <v>-4.332932537196024</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.020526588858194</v>
       </c>
       <c r="E29">
-        <v>-26.05488974454553</v>
+        <v>-28.57777959827682</v>
       </c>
       <c r="F29">
-        <v>7.033972956834979</v>
+        <v>4.992634628952402</v>
       </c>
       <c r="G29">
-        <v>-0.1252788149654342</v>
+        <v>-4.661643224881338</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.308333380120241</v>
       </c>
       <c r="E30">
-        <v>-25.27960593748435</v>
+        <v>-26.9990765751448</v>
       </c>
       <c r="F30">
-        <v>6.018891899216318</v>
+        <v>5.241209942027947</v>
       </c>
       <c r="G30">
-        <v>-1.024909633625761</v>
+        <v>-3.049520105804606</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.586158684649309</v>
       </c>
       <c r="E31">
-        <v>-26.11431238047418</v>
+        <v>-28.53674709529332</v>
       </c>
       <c r="F31">
-        <v>6.648302557483502</v>
+        <v>4.876282922756896</v>
       </c>
       <c r="G31">
-        <v>-1.347389874606168</v>
+        <v>-4.334620915421052</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.843727695333818</v>
       </c>
       <c r="E32">
-        <v>-25.44957315241424</v>
+        <v>-28.04273586579656</v>
       </c>
       <c r="F32">
-        <v>6.571519743585251</v>
+        <v>4.84984453620455</v>
       </c>
       <c r="G32">
-        <v>-1.15319327327252</v>
+        <v>-4.348750323782662</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.071733694949504</v>
       </c>
       <c r="E33">
-        <v>-25.28811494014477</v>
+        <v>-28.43593873540857</v>
       </c>
       <c r="F33">
-        <v>6.747117888077347</v>
+        <v>4.323832453450493</v>
       </c>
       <c r="G33">
-        <v>-1.862159842689602</v>
+        <v>-3.829958042869013</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.26056256588301</v>
       </c>
       <c r="E34">
-        <v>-25.07214295777095</v>
+        <v>-26.97614891124397</v>
       </c>
       <c r="F34">
-        <v>6.423118580778998</v>
+        <v>5.055944856628009</v>
       </c>
       <c r="G34">
-        <v>-1.179439278307862</v>
+        <v>-3.246990836676593</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.404585657061245</v>
       </c>
       <c r="E35">
-        <v>-24.30771390290615</v>
+        <v>-27.98458120259006</v>
       </c>
       <c r="F35">
-        <v>6.848196334424354</v>
+        <v>4.947253535945484</v>
       </c>
       <c r="G35">
-        <v>-1.694858113316993</v>
+        <v>-4.479553288584805</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.499744866756352</v>
       </c>
       <c r="E36">
-        <v>-23.30164094651806</v>
+        <v>-27.08561118495738</v>
       </c>
       <c r="F36">
-        <v>6.700471414043993</v>
+        <v>5.477330991784475</v>
       </c>
       <c r="G36">
-        <v>-2.198411953113376</v>
+        <v>-4.366812660244925</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.547033865634516</v>
       </c>
       <c r="E37">
-        <v>-25.2449766967477</v>
+        <v>-26.40673406104549</v>
       </c>
       <c r="F37">
-        <v>6.878426112938262</v>
+        <v>5.843908232619413</v>
       </c>
       <c r="G37">
-        <v>-1.660249670249452</v>
+        <v>-5.431974066414351</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.548299724061589</v>
       </c>
       <c r="E38">
-        <v>-23.06917626180831</v>
+        <v>-27.14861584382609</v>
       </c>
       <c r="F38">
-        <v>6.611129812236308</v>
+        <v>5.682164347475583</v>
       </c>
       <c r="G38">
-        <v>-2.551028090137768</v>
+        <v>-5.572821226382644</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.506725769381132</v>
       </c>
       <c r="E39">
-        <v>-22.24259390118824</v>
+        <v>-25.57486244278446</v>
       </c>
       <c r="F39">
-        <v>6.628248089476292</v>
+        <v>5.95649863726575</v>
       </c>
       <c r="G39">
-        <v>-3.421281127682603</v>
+        <v>-5.713122146336957</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.428940195277068</v>
       </c>
       <c r="E40">
-        <v>-21.05249734655045</v>
+        <v>-24.93063720197927</v>
       </c>
       <c r="F40">
-        <v>6.905379203913126</v>
+        <v>5.991101027812187</v>
       </c>
       <c r="G40">
-        <v>-3.332561817775674</v>
+        <v>-5.840074946676928</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.322100641953597</v>
       </c>
       <c r="E41">
-        <v>-21.03263545955281</v>
+        <v>-26.35160894695012</v>
       </c>
       <c r="F41">
-        <v>6.902340072261397</v>
+        <v>5.640452701074739</v>
       </c>
       <c r="G41">
-        <v>-3.031954351173233</v>
+        <v>-6.182931595451548</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.198137125382779</v>
       </c>
       <c r="E42">
-        <v>-19.45275050470479</v>
+        <v>-21.8305389942823</v>
       </c>
       <c r="F42">
-        <v>6.799738100823737</v>
+        <v>6.193813801282521</v>
       </c>
       <c r="G42">
-        <v>-3.128013140540725</v>
+        <v>-6.351226488485938</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.066270694268376</v>
       </c>
       <c r="E43">
-        <v>-20.44174658560996</v>
+        <v>-22.27811977977842</v>
       </c>
       <c r="F43">
-        <v>7.0759284939468</v>
+        <v>6.111399329148967</v>
       </c>
       <c r="G43">
-        <v>-3.035705199269227</v>
+        <v>-7.173145561157414</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.934717388174477</v>
       </c>
       <c r="E44">
-        <v>-19.45902244120541</v>
+        <v>-22.64706814260534</v>
       </c>
       <c r="F44">
-        <v>6.527495886547865</v>
+        <v>6.402676104822506</v>
       </c>
       <c r="G44">
-        <v>-3.132823363209286</v>
+        <v>-7.093142917655387</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.808762386126893</v>
       </c>
       <c r="E45">
-        <v>-17.97150929916585</v>
+        <v>-20.0465104311685</v>
       </c>
       <c r="F45">
-        <v>6.916222838316139</v>
+        <v>6.443656079090417</v>
       </c>
       <c r="G45">
-        <v>-4.183736181377689</v>
+        <v>-7.435430152597252</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.695166752242833</v>
       </c>
       <c r="E46">
-        <v>-17.84016996752139</v>
+        <v>-21.79415270563067</v>
       </c>
       <c r="F46">
-        <v>7.141598443436412</v>
+        <v>5.914155092204646</v>
       </c>
       <c r="G46">
-        <v>-2.007658319140571</v>
+        <v>-7.147161089219675</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.599688914587305</v>
       </c>
       <c r="E47">
-        <v>-17.46818752710932</v>
+        <v>-21.71781169080936</v>
       </c>
       <c r="F47">
-        <v>7.365349166287444</v>
+        <v>5.635869456155457</v>
       </c>
       <c r="G47">
-        <v>-2.776479551907675</v>
+        <v>-7.884843330644395</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.524783553188872</v>
       </c>
       <c r="E48">
-        <v>-18.38600052508792</v>
+        <v>-20.06189365737256</v>
       </c>
       <c r="F48">
-        <v>7.653491787954327</v>
+        <v>6.646362517737089</v>
       </c>
       <c r="G48">
-        <v>-3.227895610006076</v>
+        <v>-8.470846307096327</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.470404830951154</v>
       </c>
       <c r="E49">
-        <v>-16.24279604605575</v>
+        <v>-18.67355862457499</v>
       </c>
       <c r="F49">
-        <v>7.422411674126643</v>
+        <v>6.82164233734018</v>
       </c>
       <c r="G49">
-        <v>-1.819493531779475</v>
+        <v>-7.594687256309432</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.432107652003273</v>
       </c>
       <c r="E50">
-        <v>-16.12878718443864</v>
+        <v>-19.5220678563402</v>
       </c>
       <c r="F50">
-        <v>7.648374834141543</v>
+        <v>5.993389482859997</v>
       </c>
       <c r="G50">
-        <v>-4.019625817904938</v>
+        <v>-6.181915257970992</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.408716478269461</v>
       </c>
       <c r="E51">
-        <v>-15.06362669919846</v>
+        <v>-19.98633606855458</v>
       </c>
       <c r="F51">
-        <v>7.721841367852863</v>
+        <v>6.69788522228408</v>
       </c>
       <c r="G51">
-        <v>-3.600024102438933</v>
+        <v>-8.209402594223464</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.396828196757938</v>
       </c>
       <c r="E52">
-        <v>-14.54303785575069</v>
+        <v>-17.06095997349556</v>
       </c>
       <c r="F52">
-        <v>7.637893868393165</v>
+        <v>7.2358843751121</v>
       </c>
       <c r="G52">
-        <v>-4.439773773384923</v>
+        <v>-7.358148777528505</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.394784228243064</v>
       </c>
       <c r="E53">
-        <v>-14.71199522097687</v>
+        <v>-18.02904808990731</v>
       </c>
       <c r="F53">
-        <v>7.487494068721626</v>
+        <v>7.482681186444606</v>
       </c>
       <c r="G53">
-        <v>-4.006324045928146</v>
+        <v>-7.88908745002574</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.399699864996632</v>
       </c>
       <c r="E54">
-        <v>-12.74775603472783</v>
+        <v>-17.20722968394331</v>
       </c>
       <c r="F54">
-        <v>7.744135196024504</v>
+        <v>6.675779855116376</v>
       </c>
       <c r="G54">
-        <v>-3.632162878534178</v>
+        <v>-7.998765823741794</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.40735187324918</v>
       </c>
       <c r="E55">
-        <v>-12.67794960789959</v>
+        <v>-15.53215620545406</v>
       </c>
       <c r="F55">
-        <v>7.875536859534431</v>
+        <v>6.71370327696749</v>
       </c>
       <c r="G55">
-        <v>-4.172321420358283</v>
+        <v>-8.16849087244915</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.415691724862079</v>
       </c>
       <c r="E56">
-        <v>-12.478642409874</v>
+        <v>-16.02863998175901</v>
       </c>
       <c r="F56">
-        <v>7.691969506875845</v>
+        <v>6.678147495459958</v>
       </c>
       <c r="G56">
-        <v>-3.037718010957104</v>
+        <v>-7.637790559230743</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.421599945479072</v>
       </c>
       <c r="E57">
-        <v>-11.30773299960671</v>
+        <v>-15.64909046128012</v>
       </c>
       <c r="F57">
-        <v>8.08541906968396</v>
+        <v>7.111077263034063</v>
       </c>
       <c r="G57">
-        <v>-4.590625401972893</v>
+        <v>-7.444040881544897</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.424771250964488</v>
       </c>
       <c r="E58">
-        <v>-11.91869207035155</v>
+        <v>-15.4567254139083</v>
       </c>
       <c r="F58">
-        <v>7.644814663243635</v>
+        <v>6.775855815618911</v>
       </c>
       <c r="G58">
-        <v>-4.438962689727801</v>
+        <v>-8.894179007385091</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.422518174522822</v>
       </c>
       <c r="E59">
-        <v>-10.66472138983557</v>
+        <v>-12.77709601782352</v>
       </c>
       <c r="F59">
-        <v>8.217591997974704</v>
+        <v>7.198833575220394</v>
       </c>
       <c r="G59">
-        <v>-3.514042613692982</v>
+        <v>-8.369755488509142</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.411171778295905</v>
       </c>
       <c r="E60">
-        <v>-9.791464047618442</v>
+        <v>-13.83247952768114</v>
       </c>
       <c r="F60">
-        <v>7.794498627841394</v>
+        <v>6.878278828288126</v>
       </c>
       <c r="G60">
-        <v>-3.549167501864649</v>
+        <v>-8.150193487253597</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.385695341286915</v>
       </c>
       <c r="E61">
-        <v>-10.09427404756334</v>
+        <v>-12.97184757099739</v>
       </c>
       <c r="F61">
-        <v>7.662465065671207</v>
+        <v>6.912534387239082</v>
       </c>
       <c r="G61">
-        <v>-4.683777532356905</v>
+        <v>-7.93079039218394</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.342752265390812</v>
       </c>
       <c r="E62">
-        <v>-10.43627799004463</v>
+        <v>-11.75546322474507</v>
       </c>
       <c r="F62">
-        <v>7.772329912437073</v>
+        <v>6.813416568815388</v>
       </c>
       <c r="G62">
-        <v>-4.409776920253587</v>
+        <v>-8.530734075901742</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.28006540162136</v>
       </c>
       <c r="E63">
-        <v>-6.840963978764866</v>
+        <v>-12.2878849707749</v>
       </c>
       <c r="F63">
-        <v>7.940019029587464</v>
+        <v>6.643758905212106</v>
       </c>
       <c r="G63">
-        <v>-4.477434539439672</v>
+        <v>-8.008111493799158</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.194335688718243</v>
       </c>
       <c r="E64">
-        <v>-7.09505665533525</v>
+        <v>-10.81429235783491</v>
       </c>
       <c r="F64">
-        <v>7.750693322220339</v>
+        <v>6.299477076254725</v>
       </c>
       <c r="G64">
-        <v>-4.524606502828747</v>
+        <v>-8.80333432724195</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.082762045104057</v>
       </c>
       <c r="E65">
-        <v>-7.647168206350419</v>
+        <v>-11.51046372398209</v>
       </c>
       <c r="F65">
-        <v>7.060267226149019</v>
+        <v>6.084740807474375</v>
       </c>
       <c r="G65">
-        <v>-4.336918434025306</v>
+        <v>-8.711486551800411</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.941395405564859</v>
       </c>
       <c r="E66">
-        <v>-7.539490151396034</v>
+        <v>-10.37433299409371</v>
       </c>
       <c r="F66">
-        <v>7.020044263308688</v>
+        <v>6.196124428213147</v>
       </c>
       <c r="G66">
-        <v>-4.85886897538342</v>
+        <v>-8.883085369282993</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.772716841170584</v>
       </c>
       <c r="E67">
-        <v>-7.727385594922292</v>
+        <v>-10.10898705961426</v>
       </c>
       <c r="F67">
-        <v>7.261355117350113</v>
+        <v>5.66580941648684</v>
       </c>
       <c r="G67">
-        <v>-5.025452316374007</v>
+        <v>-8.922047179734676</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.578854640864908</v>
       </c>
       <c r="E68">
-        <v>-7.509253530446819</v>
+        <v>-8.953270679642705</v>
       </c>
       <c r="F68">
-        <v>7.474775326514732</v>
+        <v>5.64115745020711</v>
       </c>
       <c r="G68">
-        <v>-4.207075527429551</v>
+        <v>-8.35536454704993</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.363557675283679</v>
       </c>
       <c r="E69">
-        <v>-7.38070373879108</v>
+        <v>-8.97415600176608</v>
       </c>
       <c r="F69">
-        <v>6.987853856871467</v>
+        <v>5.363736517587751</v>
       </c>
       <c r="G69">
-        <v>-4.063152870655276</v>
+        <v>-8.239680843725637</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.130251971511659</v>
       </c>
       <c r="E70">
-        <v>-8.530071198203887</v>
+        <v>-8.85075961353107</v>
       </c>
       <c r="F70">
-        <v>7.165121227398434</v>
+        <v>5.617059780997782</v>
       </c>
       <c r="G70">
-        <v>-5.037092194490084</v>
+        <v>-8.017331363126027</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.8810791774623</v>
       </c>
       <c r="E71">
-        <v>-6.26058116451981</v>
+        <v>-12.69617671578046</v>
       </c>
       <c r="F71">
-        <v>6.555725444490574</v>
+        <v>5.882458802013041</v>
       </c>
       <c r="G71">
-        <v>-3.895367801633933</v>
+        <v>-9.382054103507485</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.621423263677795</v>
       </c>
       <c r="E72">
-        <v>-7.752527682612878</v>
+        <v>-10.84809288782817</v>
       </c>
       <c r="F72">
-        <v>6.833151128227679</v>
+        <v>4.96082272822897</v>
       </c>
       <c r="G72">
-        <v>-4.020711676841819</v>
+        <v>-8.51221157360952</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.356750543752064</v>
       </c>
       <c r="E73">
-        <v>-8.658738730183824</v>
+        <v>-9.459182738831622</v>
       </c>
       <c r="F73">
-        <v>6.574015664107984</v>
+        <v>4.760666056106155</v>
       </c>
       <c r="G73">
-        <v>-4.194124673279922</v>
+        <v>-7.884187842627619</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.093236538811232</v>
       </c>
       <c r="E74">
-        <v>-8.000547675538975</v>
+        <v>-12.42552793823804</v>
       </c>
       <c r="F74">
-        <v>5.854291008601034</v>
+        <v>4.356513808721501</v>
       </c>
       <c r="G74">
-        <v>-3.625992021648976</v>
+        <v>-6.395253433612706</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.836118734946024</v>
       </c>
       <c r="E75">
-        <v>-7.513768419032466</v>
+        <v>-10.29696401567266</v>
       </c>
       <c r="F75">
-        <v>6.397301006945504</v>
+        <v>4.671262689767767</v>
       </c>
       <c r="G75">
-        <v>-3.87389891381176</v>
+        <v>-6.354563518389524</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.590227565870853</v>
       </c>
       <c r="E76">
-        <v>-8.014468204638554</v>
+        <v>-7.940699363053604</v>
       </c>
       <c r="F76">
-        <v>6.205531641350857</v>
+        <v>4.828787582352867</v>
       </c>
       <c r="G76">
-        <v>-3.438194704842739</v>
+        <v>-8.147819826101941</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.360561934112761</v>
       </c>
       <c r="E77">
-        <v>-8.621428632834627</v>
+        <v>-11.52012295904045</v>
       </c>
       <c r="F77">
-        <v>6.148313930331946</v>
+        <v>4.066502414074399</v>
       </c>
       <c r="G77">
-        <v>-3.779650992854248</v>
+        <v>-7.285700798947095</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.153847215116417</v>
       </c>
       <c r="E78">
-        <v>-9.068669782780168</v>
+        <v>-11.85630328394788</v>
       </c>
       <c r="F78">
-        <v>5.267822536230991</v>
+        <v>4.021674034431969</v>
       </c>
       <c r="G78">
-        <v>-2.552454935265194</v>
+        <v>-5.509583185491485</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.977199363767008</v>
       </c>
       <c r="E79">
-        <v>-9.078211277514329</v>
+        <v>-10.20764892281938</v>
       </c>
       <c r="F79">
-        <v>5.092971900930984</v>
+        <v>4.395925914133127</v>
       </c>
       <c r="G79">
-        <v>-1.660176838247588</v>
+        <v>-4.684462815283535</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.836539714599252</v>
       </c>
       <c r="E80">
-        <v>-8.843867276091396</v>
+        <v>-11.98109897065126</v>
       </c>
       <c r="F80">
-        <v>5.744218696360247</v>
+        <v>4.012171798939333</v>
       </c>
       <c r="G80">
-        <v>-3.126202272130744</v>
+        <v>-4.576813805983054</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.738021274250503</v>
       </c>
       <c r="E81">
-        <v>-9.777960138127568</v>
+        <v>-12.29312894367578</v>
       </c>
       <c r="F81">
-        <v>5.648442497418131</v>
+        <v>4.131410601018684</v>
       </c>
       <c r="G81">
-        <v>-1.713324336335048</v>
+        <v>-4.048990356838273</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.686128003019772</v>
       </c>
       <c r="E82">
-        <v>-11.52949237176233</v>
+        <v>-13.37617690124625</v>
       </c>
       <c r="F82">
-        <v>5.083309711140887</v>
+        <v>3.730666488764055</v>
       </c>
       <c r="G82">
-        <v>-1.378611629587034</v>
+        <v>-6.840141095907665</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.687898048771582</v>
       </c>
       <c r="E83">
-        <v>-11.57151661055351</v>
+        <v>-11.61011732299489</v>
       </c>
       <c r="F83">
-        <v>5.431462117355603</v>
+        <v>3.938903228467442</v>
       </c>
       <c r="G83">
-        <v>-2.14202343094297</v>
+        <v>-5.117793363100898</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.74888946407707</v>
       </c>
       <c r="E84">
-        <v>-13.44570256268601</v>
+        <v>-12.17287531640209</v>
       </c>
       <c r="F84">
-        <v>5.222403434282104</v>
+        <v>3.150612025351542</v>
       </c>
       <c r="G84">
-        <v>-1.214517818841979</v>
+        <v>-4.976191398749651</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.875453432203809</v>
       </c>
       <c r="E85">
-        <v>-14.45443826179062</v>
+        <v>-15.72076714787353</v>
       </c>
       <c r="F85">
-        <v>4.952068001928421</v>
+        <v>3.889347486667426</v>
       </c>
       <c r="G85">
-        <v>-0.332330264628072</v>
+        <v>-3.040091672108761</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.072111482087734</v>
       </c>
       <c r="E86">
-        <v>-14.59625648228883</v>
+        <v>-16.04472512143425</v>
       </c>
       <c r="F86">
-        <v>5.056271100046589</v>
+        <v>3.540132413783451</v>
       </c>
       <c r="G86">
-        <v>0.3284016562818285</v>
+        <v>-4.277924512515494</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.341112354407097</v>
       </c>
       <c r="E87">
-        <v>-16.04963398725857</v>
+        <v>-15.80064942936884</v>
       </c>
       <c r="F87">
-        <v>4.533386836475525</v>
+        <v>2.80135735981968</v>
       </c>
       <c r="G87">
-        <v>-0.4202682857877326</v>
+        <v>-2.599471303013924</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.683400368522114</v>
       </c>
       <c r="E88">
-        <v>-17.50043931899195</v>
+        <v>-17.9530014258965</v>
       </c>
       <c r="F88">
-        <v>4.415997802905406</v>
+        <v>2.706002426651071</v>
       </c>
       <c r="G88">
-        <v>0.5634901161165541</v>
+        <v>-2.942649074705853</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.095278277389109</v>
       </c>
       <c r="E89">
-        <v>-20.26696560280991</v>
+        <v>-19.32262933256839</v>
       </c>
       <c r="F89">
-        <v>4.503885562682719</v>
+        <v>3.385518372670929</v>
       </c>
       <c r="G89">
-        <v>0.6584531149105481</v>
+        <v>-2.113820893493919</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.576332774982013</v>
       </c>
       <c r="E90">
-        <v>-19.92596245308432</v>
+        <v>-21.9685714105101</v>
       </c>
       <c r="F90">
-        <v>4.29030856663247</v>
+        <v>3.036303299786953</v>
       </c>
       <c r="G90">
-        <v>0.5047709698865011</v>
+        <v>-0.6690590936095016</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.120586138050577</v>
       </c>
       <c r="E91">
-        <v>-22.50000142073224</v>
+        <v>-23.09010686867176</v>
       </c>
       <c r="F91">
-        <v>3.770260720355957</v>
+        <v>1.74032665877046</v>
       </c>
       <c r="G91">
-        <v>0.9260577530319952</v>
+        <v>-0.9040647898057453</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.718422624266722</v>
       </c>
       <c r="E92">
-        <v>-23.71470117465371</v>
+        <v>-25.71301712781047</v>
       </c>
       <c r="F92">
-        <v>3.209030185454357</v>
+        <v>2.581830380645126</v>
       </c>
       <c r="G92">
-        <v>0.43305131132373</v>
+        <v>-3.275944867963059</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.356844833166942</v>
       </c>
       <c r="E93">
-        <v>-25.28186564601418</v>
+        <v>-26.76446086528141</v>
       </c>
       <c r="F93">
-        <v>3.579965784968584</v>
+        <v>2.32654965672361</v>
       </c>
       <c r="G93">
-        <v>1.148539655453176</v>
+        <v>-1.333535241524318</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.014106690684143</v>
       </c>
       <c r="E94">
-        <v>-26.95021434060204</v>
+        <v>-27.65821408085725</v>
       </c>
       <c r="F94">
-        <v>3.411757212277929</v>
+        <v>1.976512640469522</v>
       </c>
       <c r="G94">
-        <v>1.036312161671883</v>
+        <v>-1.554908111189843</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.676272889395394</v>
       </c>
       <c r="E95">
-        <v>-29.72611003714187</v>
+        <v>-29.71283028711438</v>
       </c>
       <c r="F95">
-        <v>2.794981359804121</v>
+        <v>1.616856194485054</v>
       </c>
       <c r="G95">
-        <v>-0.2791827665406124</v>
+        <v>-3.352968020479742</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.324978254225204</v>
       </c>
       <c r="E96">
-        <v>-32.1991391278117</v>
+        <v>-30.88852855864478</v>
       </c>
       <c r="F96">
-        <v>2.602705208316533</v>
+        <v>1.177360382185538</v>
       </c>
       <c r="G96">
-        <v>0.477035219358487</v>
+        <v>-2.488220420166715</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.939726083801578</v>
       </c>
       <c r="E97">
-        <v>-33.27781031525376</v>
+        <v>-32.41780328798308</v>
       </c>
       <c r="F97">
-        <v>2.648512318214704</v>
+        <v>0.6870260262944996</v>
       </c>
       <c r="G97">
-        <v>0.4925120197545799</v>
+        <v>-0.8064136280338631</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.5040070761556</v>
       </c>
       <c r="E98">
-        <v>-35.33123100437286</v>
+        <v>-35.77902462814733</v>
       </c>
       <c r="F98">
-        <v>2.170153946456219</v>
+        <v>1.480229885160093</v>
       </c>
       <c r="G98">
-        <v>0.3401276085819271</v>
+        <v>-1.549170935770286</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.99635049928221</v>
       </c>
       <c r="E99">
-        <v>-39.21078374369207</v>
+        <v>-37.58539441777798</v>
       </c>
       <c r="F99">
-        <v>1.734440023882772</v>
+        <v>0.4182196620021736</v>
       </c>
       <c r="G99">
-        <v>0.5375553023619036</v>
+        <v>-2.116701068113085</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.41272922609141</v>
       </c>
       <c r="E100">
-        <v>-41.34538412210966</v>
+        <v>-38.95018591420967</v>
       </c>
       <c r="F100">
-        <v>1.359454888342766</v>
+        <v>0.1291188982564488</v>
       </c>
       <c r="G100">
-        <v>-0.4820132706406795</v>
+        <v>-4.426286610857932</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.73771489030279</v>
       </c>
       <c r="E101">
-        <v>-41.96118186733171</v>
+        <v>-42.37998872898309</v>
       </c>
       <c r="F101">
-        <v>1.516574352213513</v>
+        <v>0.2772840888813017</v>
       </c>
       <c r="G101">
-        <v>-0.6207052654629066</v>
+        <v>-3.454965928544687</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.98651315239533</v>
       </c>
       <c r="E102">
-        <v>-44.45083045760969</v>
+        <v>-45.18422135162592</v>
       </c>
       <c r="F102">
-        <v>1.203323656963252</v>
+        <v>-0.3021954892839075</v>
       </c>
       <c r="G102">
-        <v>0.6232951212834881</v>
+        <v>-4.65577693818575</v>
       </c>
     </row>
   </sheetData>
